--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_109_R11.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_109_R11.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.2233</v>
+        <v>2.8029</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1893</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>3.034</v>
+        <v>2.7315</v>
       </c>
       <c r="G2" t="n">
         <v>-0.8120000000000001</v>
@@ -610,13 +610,13 @@
         <v>3.0154</v>
       </c>
       <c r="S2" t="n">
-        <v>1.1075</v>
+        <v>0.6871</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6844</v>
+        <v>0.5665</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4231</v>
+        <v>0.1206</v>
       </c>
       <c r="V2" t="n">
         <v>1.0722</v>
@@ -643,10 +643,10 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1307</v>
+        <v>2.5592</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6105</v>
+        <v>1.0391</v>
       </c>
       <c r="F3" t="n">
         <v>1.5202</v>
@@ -688,10 +688,10 @@
         <v>2.3195</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1652</v>
+        <v>0.5937</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0272</v>
+        <v>0.4013</v>
       </c>
       <c r="U3" t="n">
         <v>0.1924</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>K. PUNTER</t>
+          <t>W. CLYBURN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5736</v>
+        <v>1.4772</v>
       </c>
       <c r="E4" t="n">
-        <v>2.1179</v>
+        <v>2.8254</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.5442</v>
+        <v>-1.3481</v>
       </c>
       <c r="G4" t="n">
-        <v>3.9213</v>
+        <v>0.6722</v>
       </c>
       <c r="H4" t="n">
-        <v>-2.1716</v>
+        <v>0.3443</v>
       </c>
       <c r="I4" t="n">
-        <v>6.0929</v>
+        <v>0.3279</v>
       </c>
       <c r="J4" t="n">
-        <v>4.3792</v>
+        <v>2.4634</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.717</v>
+        <v>1.6069</v>
       </c>
       <c r="L4" t="n">
-        <v>6.0962</v>
+        <v>0.8564000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.458</v>
+        <v>-1.7912</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.4547</v>
+        <v>-1.2626</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.0033</v>
+        <v>-0.5286</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.9278</v>
+        <v>0.6959</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3917</v>
+        <v>0.6959</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1885</v>
+        <v>0.1092</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4525</v>
+        <v>0.362</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.264</v>
+        <v>-0.2528</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.6083</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.3943</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.214</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>W. CLYBURN</t>
+          <t>J. MARCOS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,58 +799,58 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.227</v>
+        <v>1.2921</v>
       </c>
       <c r="E5" t="n">
-        <v>2.676</v>
+        <v>0.4016</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.449</v>
+        <v>0.8905</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6722</v>
+        <v>0.9402</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3443</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3279</v>
+        <v>0.9402</v>
       </c>
       <c r="J5" t="n">
-        <v>2.4634</v>
+        <v>0.6257</v>
       </c>
       <c r="K5" t="n">
-        <v>1.6069</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8564000000000001</v>
+        <v>0.6257</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.7912</v>
+        <v>0.3145</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.2626</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.5286</v>
+        <v>0.3145</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6959</v>
+        <v>0.4639</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.6959</v>
+        <v>0.4639</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.141</v>
+        <v>-0.112</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2126</v>
+        <v>-0.224</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3536</v>
+        <v>0.112</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. MARCOS</t>
+          <t>M. CALE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2249</v>
+        <v>1.2538</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4016</v>
+        <v>0.3489</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8232</v>
+        <v>0.9048</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9402</v>
+        <v>0.1668</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>0.4946</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9402</v>
+        <v>-0.3279</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6257</v>
+        <v>1.0211</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>0.8739</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6257</v>
+        <v>0.1472</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3145</v>
+        <v>-0.8542999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>-0.3792</v>
       </c>
       <c r="O6" t="n">
-        <v>0.3145</v>
+        <v>-0.4751</v>
       </c>
       <c r="P6" t="n">
-        <v>0.4639</v>
+        <v>1.3917</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.4639</v>
+        <v>1.3917</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1792</v>
+        <v>-0.5573</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.224</v>
+        <v>-0.6721</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0448</v>
+        <v>0.1149</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.2525</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>0.2525</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. CALE</t>
+          <t>K. PUNTER</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2202</v>
+        <v>1.2191</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3489</v>
+        <v>1.5281</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8712</v>
+        <v>-0.309</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1668</v>
+        <v>3.9213</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4946</v>
+        <v>-2.1716</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3279</v>
+        <v>6.0929</v>
       </c>
       <c r="J7" t="n">
-        <v>1.0211</v>
+        <v>4.3792</v>
       </c>
       <c r="K7" t="n">
-        <v>0.8739</v>
+        <v>-1.717</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1472</v>
+        <v>6.0962</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.8542999999999999</v>
+        <v>-0.458</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3792</v>
+        <v>-0.4547</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.4751</v>
+        <v>-0.0033</v>
       </c>
       <c r="P7" t="n">
-        <v>1.3917</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R7" t="n">
         <v>1.3917</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5909</v>
+        <v>-0.1661</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6721</v>
+        <v>-0.1373</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0813</v>
+        <v>-0.0288</v>
       </c>
       <c r="V7" t="n">
-        <v>0.2525</v>
+        <v>-1.6083</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>-0.3943</v>
       </c>
       <c r="X7" t="n">
-        <v>0.2525</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>T. SHENGELIA</t>
+          <t>J. PARRA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4274</v>
+        <v>0.9833</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.4639</v>
+        <v>2.0304</v>
       </c>
       <c r="F8" t="n">
-        <v>1.8913</v>
+        <v>-1.0472</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.746</v>
+        <v>-0.5931</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.6589</v>
+        <v>-0.9075</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0871</v>
+        <v>0.3144</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.6105</v>
+        <v>1.3658</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.6868</v>
+        <v>0.1547</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.9236</v>
+        <v>1.211</v>
       </c>
       <c r="M8" t="n">
-        <v>0.8645</v>
+        <v>-1.9588</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0279</v>
+        <v>-1.0622</v>
       </c>
       <c r="O8" t="n">
-        <v>0.8366</v>
+        <v>-0.8966</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.3917</v>
+        <v>1.6237</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.4793</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.0876</v>
+        <v>1.6237</v>
       </c>
       <c r="S8" t="n">
-        <v>2.3511</v>
+        <v>0.0944</v>
       </c>
       <c r="T8" t="n">
-        <v>2.3397</v>
+        <v>0.6647</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0114</v>
+        <v>-0.5702</v>
       </c>
       <c r="V8" t="n">
-        <v>1.214</v>
+        <v>-0.1418</v>
       </c>
       <c r="W8" t="n">
-        <v>2.2862</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.0722</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. PARRA</t>
+          <t>D. BRIZUELA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1262</v>
+        <v>-0.6176</v>
       </c>
       <c r="E9" t="n">
-        <v>1.1734</v>
+        <v>0.8239</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.0472</v>
+        <v>-1.4415</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.5931</v>
+        <v>-0.2177</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.9075</v>
+        <v>-0.9002</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3144</v>
+        <v>0.6825</v>
       </c>
       <c r="J9" t="n">
-        <v>1.3658</v>
+        <v>1.3623</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1547</v>
+        <v>0.1512</v>
       </c>
       <c r="L9" t="n">
         <v>1.211</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.9588</v>
+        <v>-1.58</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.0622</v>
+        <v>-1.0514</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.8966</v>
+        <v>-0.5286</v>
       </c>
       <c r="P9" t="n">
-        <v>1.6237</v>
+        <v>0.4639</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R9" t="n">
         <v>1.6237</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7625999999999999</v>
+        <v>0.2084</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1924</v>
+        <v>0.6214</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5702</v>
+        <v>-0.4129</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.1418</v>
+        <v>-1.0722</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.1418</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. BRIZUELA</t>
+          <t>T. SHENGELIA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.282</v>
+        <v>-1.0313</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1595</v>
+        <v>-2.9225</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.4415</v>
+        <v>1.8913</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.2177</v>
+        <v>-1.746</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.9002</v>
+        <v>-1.6589</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6825</v>
+        <v>-0.0871</v>
       </c>
       <c r="J10" t="n">
-        <v>1.3623</v>
+        <v>-2.6105</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1512</v>
+        <v>-1.6868</v>
       </c>
       <c r="L10" t="n">
-        <v>1.211</v>
+        <v>-0.9236</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.58</v>
+        <v>0.8645</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.0514</v>
+        <v>0.0279</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.5286</v>
+        <v>0.8366</v>
       </c>
       <c r="P10" t="n">
-        <v>0.4639</v>
+        <v>-1.3917</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1598</v>
+        <v>-3.4793</v>
       </c>
       <c r="R10" t="n">
-        <v>1.6237</v>
+        <v>2.0876</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.456</v>
+        <v>0.8924</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0431</v>
+        <v>0.881</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4129</v>
+        <v>0.0114</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.0722</v>
+        <v>1.214</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>2.2862</v>
       </c>
       <c r="X10" t="n">
         <v>-1.0722</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>W. HERNANGOMEZ</t>
+          <t>N. LAPROVITTOLA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.6186</v>
+        <v>-2.4742</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.192</v>
+        <v>1.0024</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.4266</v>
+        <v>-3.4766</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.3753</v>
+        <v>-0.6387</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.1909</v>
+        <v>0.449</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.1844</v>
+        <v>-1.0877</v>
       </c>
       <c r="J11" t="n">
-        <v>0.2582</v>
+        <v>0.8056</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0742</v>
+        <v>1.3647</v>
       </c>
       <c r="L11" t="n">
-        <v>0.184</v>
+        <v>-0.5591</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.6335</v>
+        <v>-1.4443</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2651</v>
+        <v>-0.9157</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.3684</v>
+        <v>-0.5286</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.1598</v>
+        <v>0.4639</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>0.4639</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2254</v>
+        <v>-0.5493</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4323</v>
+        <v>0.1968</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2069</v>
+        <v>-0.7461</v>
       </c>
       <c r="V11" t="n">
-        <v>0.1418</v>
+        <v>-1.7501</v>
       </c>
       <c r="W11" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-1.7501</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>N. LAPROVITTOLA</t>
+          <t>W. HERNANGOMEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.2634</v>
+        <v>-2.7284</v>
       </c>
       <c r="E12" t="n">
-        <v>0.3812</v>
+        <v>-0.9994</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.6447</v>
+        <v>-1.7291</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.6387</v>
+        <v>-1.3753</v>
       </c>
       <c r="H12" t="n">
-        <v>0.449</v>
+        <v>-0.1909</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.0877</v>
+        <v>-1.1844</v>
       </c>
       <c r="J12" t="n">
-        <v>0.8056</v>
+        <v>0.2582</v>
       </c>
       <c r="K12" t="n">
-        <v>1.3647</v>
+        <v>0.0742</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.5591</v>
+        <v>0.184</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.4443</v>
+        <v>-1.6335</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.9157</v>
+        <v>-0.2651</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.5286</v>
+        <v>-1.3684</v>
       </c>
       <c r="P12" t="n">
-        <v>0.4639</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R12" t="n">
-        <v>0.4639</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.3385</v>
+        <v>-0.3352</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4244</v>
+        <v>-0.2396</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.9142</v>
+        <v>-0.0955</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.7501</v>
+        <v>0.1418</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.7501</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1423,28 +1423,28 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.9893</v>
+        <v>4.736099999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>5.402400000000001</v>
+        <v>6.1493</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.4133</v>
+        <v>-1.4132</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8709</v>
+        <v>0.8709000000000005</v>
       </c>
       <c r="H13" t="n">
         <v>-7.2928</v>
       </c>
       <c r="I13" t="n">
-        <v>8.163599999999999</v>
+        <v>8.163600000000001</v>
       </c>
       <c r="J13" t="n">
         <v>11.0608</v>
       </c>
       <c r="K13" t="n">
-        <v>0.2376999999999998</v>
+        <v>0.2376999999999997</v>
       </c>
       <c r="L13" t="n">
         <v>10.8228</v>
@@ -1459,7 +1459,7 @@
         <v>-2.6593</v>
       </c>
       <c r="P13" t="n">
-        <v>4.6391</v>
+        <v>4.639099999999999</v>
       </c>
       <c r="Q13" t="n">
         <v>-10.438</v>
@@ -1468,10 +1468,10 @@
         <v>15.077</v>
       </c>
       <c r="S13" t="n">
-        <v>0.1187000000000002</v>
+        <v>0.8653</v>
       </c>
       <c r="T13" t="n">
-        <v>1.6737</v>
+        <v>2.4207</v>
       </c>
       <c r="U13" t="n">
         <v>-1.555</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.9085</v>
+        <v>3.1336</v>
       </c>
       <c r="E14" t="n">
-        <v>3.4275</v>
+        <v>2.248</v>
       </c>
       <c r="F14" t="n">
-        <v>0.481</v>
+        <v>0.8856000000000001</v>
       </c>
       <c r="G14" t="n">
         <v>2.106</v>
@@ -1546,13 +1546,13 @@
         <v>0.9278</v>
       </c>
       <c r="S14" t="n">
-        <v>1.0165</v>
+        <v>0.2416</v>
       </c>
       <c r="T14" t="n">
-        <v>1.8363</v>
+        <v>0.6567</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.8197</v>
+        <v>-0.4151</v>
       </c>
       <c r="V14" t="n">
         <v>-0.1418</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. DIARRA</t>
+          <t>M. MORGAN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.4143</v>
+        <v>3.0302</v>
       </c>
       <c r="E15" t="n">
-        <v>1.2546</v>
+        <v>3.9841</v>
       </c>
       <c r="F15" t="n">
-        <v>1.1597</v>
+        <v>-0.9539</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0136</v>
+        <v>0.0581</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.9233</v>
+        <v>1.0685</v>
       </c>
       <c r="I15" t="n">
-        <v>0.9370000000000001</v>
+        <v>-1.0104</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.08649999999999999</v>
+        <v>1.455</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.7121</v>
+        <v>0.6722</v>
       </c>
       <c r="L15" t="n">
-        <v>0.6257</v>
+        <v>0.7828000000000001</v>
       </c>
       <c r="M15" t="n">
-        <v>0.1001</v>
+        <v>-1.3969</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.2112</v>
+        <v>0.3963</v>
       </c>
       <c r="O15" t="n">
-        <v>0.3113</v>
+        <v>-1.7933</v>
       </c>
       <c r="P15" t="n">
-        <v>0.232</v>
+        <v>-1.8556</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R15" t="n">
-        <v>0.232</v>
+        <v>0.4639</v>
       </c>
       <c r="S15" t="n">
-        <v>2.0269</v>
+        <v>0.0029</v>
       </c>
       <c r="T15" t="n">
-        <v>1.1993</v>
+        <v>0.0237</v>
       </c>
       <c r="U15" t="n">
-        <v>0.8276</v>
+        <v>-0.0209</v>
       </c>
       <c r="V15" t="n">
-        <v>0.1418</v>
+        <v>4.8249</v>
       </c>
       <c r="W15" t="n">
-        <v>0.1418</v>
+        <v>4.8249</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. MORGAN</t>
+          <t>A. DIARRA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.717</v>
+        <v>1.4999</v>
       </c>
       <c r="E16" t="n">
-        <v>3.5123</v>
+        <v>0.4289</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.7954</v>
+        <v>1.071</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0581</v>
+        <v>0.0136</v>
       </c>
       <c r="H16" t="n">
-        <v>1.0685</v>
+        <v>-0.9233</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.0104</v>
+        <v>0.9370000000000001</v>
       </c>
       <c r="J16" t="n">
-        <v>1.455</v>
+        <v>-0.08649999999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>0.6722</v>
+        <v>-0.7121</v>
       </c>
       <c r="L16" t="n">
-        <v>0.7828000000000001</v>
+        <v>0.6257</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.3969</v>
+        <v>0.1001</v>
       </c>
       <c r="N16" t="n">
-        <v>0.3963</v>
+        <v>-0.2112</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.7933</v>
+        <v>0.3113</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.8556</v>
+        <v>0.232</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.4639</v>
+        <v>0.232</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.3104</v>
+        <v>1.1125</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4481</v>
+        <v>0.3736</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.8623</v>
+        <v>0.7389</v>
       </c>
       <c r="V16" t="n">
-        <v>4.8249</v>
+        <v>0.1418</v>
       </c>
       <c r="W16" t="n">
-        <v>4.8249</v>
+        <v>0.1418</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. ALSTON JR.</t>
+          <t>C. EDWARDS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,58 +1735,58 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8828</v>
+        <v>0.765</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6151</v>
+        <v>-0.0225</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2676</v>
+        <v>0.7876</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.6516999999999999</v>
+        <v>0.4672</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1465</v>
+        <v>1.983</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.5052</v>
+        <v>-1.5158</v>
       </c>
       <c r="J17" t="n">
-        <v>0.1275</v>
+        <v>1.2824</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0539</v>
+        <v>2.4269</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0736</v>
+        <v>-1.1445</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.7792</v>
+        <v>-0.8152</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.2004</v>
+        <v>-0.4439</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.5788</v>
+        <v>-0.3713</v>
       </c>
       <c r="P17" t="n">
-        <v>0.6959</v>
+        <v>0.4639</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R17" t="n">
-        <v>0.6959</v>
+        <v>1.6237</v>
       </c>
       <c r="S17" t="n">
-        <v>0.8386</v>
+        <v>-0.1661</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4876</v>
+        <v>-0.1452</v>
       </c>
       <c r="U17" t="n">
-        <v>0.351</v>
+        <v>-0.0209</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C. EDWARDS</t>
+          <t>D. ALSTON JR.</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4531</v>
+        <v>0.4953</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.8482</v>
+        <v>0.2613</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3951</v>
+        <v>0.234</v>
       </c>
       <c r="G18" t="n">
-        <v>0.4672</v>
+        <v>-0.6516999999999999</v>
       </c>
       <c r="H18" t="n">
-        <v>1.983</v>
+        <v>-0.1465</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.5158</v>
+        <v>-0.5052</v>
       </c>
       <c r="J18" t="n">
-        <v>1.2824</v>
+        <v>0.1275</v>
       </c>
       <c r="K18" t="n">
-        <v>2.4269</v>
+        <v>0.0539</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.1445</v>
+        <v>0.0736</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.8152</v>
+        <v>-0.7792</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4439</v>
+        <v>-0.2004</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.3713</v>
+        <v>-0.5788</v>
       </c>
       <c r="P18" t="n">
-        <v>0.4639</v>
+        <v>0.6959</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.6237</v>
+        <v>0.6959</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.3842</v>
+        <v>0.4512</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.9709</v>
+        <v>0.1338</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4134</v>
+        <v>0.3174</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. HACKETT</t>
+          <t>A. PAJOLA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,58 +1891,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.7151999999999999</v>
+        <v>-0.1988</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3965</v>
+        <v>-0.3971</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.1116</v>
+        <v>0.1984</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.3641</v>
+        <v>0.1738</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0073</v>
+        <v>1.7731</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.3714</v>
+        <v>-1.5993</v>
       </c>
       <c r="J19" t="n">
-        <v>0.9939</v>
+        <v>0.7703</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0504</v>
+        <v>1.6805</v>
       </c>
       <c r="L19" t="n">
-        <v>0.9435</v>
+        <v>-0.9102</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.3581</v>
+        <v>-0.5965</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.0431</v>
+        <v>0.0926</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.3149</v>
+        <v>-0.6891</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.4639</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q19" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R19" t="n">
-        <v>0.6959</v>
+        <v>0.4639</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1129</v>
+        <v>0.3233</v>
       </c>
       <c r="T19" t="n">
-        <v>0.5623</v>
+        <v>-0.0077</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4494</v>
+        <v>0.331</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. DIOUF</t>
+          <t>L. VILDOZA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.0067</v>
+        <v>-0.4879</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7125</v>
+        <v>-0.4032</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.7191</v>
+        <v>-0.08459999999999999</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.5035</v>
+        <v>1.4324</v>
       </c>
       <c r="H20" t="n">
-        <v>1.1932</v>
+        <v>1.3387</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.6967</v>
+        <v>0.09370000000000001</v>
       </c>
       <c r="J20" t="n">
-        <v>0.8299</v>
+        <v>3.048</v>
       </c>
       <c r="K20" t="n">
-        <v>0.6827</v>
+        <v>1.4788</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1472</v>
+        <v>1.5692</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.3334</v>
+        <v>-1.6156</v>
       </c>
       <c r="N20" t="n">
-        <v>0.5105</v>
+        <v>-0.1401</v>
       </c>
       <c r="O20" t="n">
-        <v>-2.8439</v>
+        <v>-1.4755</v>
       </c>
       <c r="P20" t="n">
-        <v>1.1598</v>
+        <v>-1.8556</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-3.4793</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1598</v>
+        <v>1.6237</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2675</v>
+        <v>-0.2065</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2592</v>
+        <v>-0.1138</v>
       </c>
       <c r="U20" t="n">
-        <v>0.5266999999999999</v>
+        <v>-0.0927</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.9304</v>
+        <v>0.1418</v>
       </c>
       <c r="W20" t="n">
         <v>0.1418</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>L. VILDOZA</t>
+          <t>D. HACKETT</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.1284</v>
+        <v>-0.6422</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.111</v>
+        <v>0.2785</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.0174</v>
+        <v>-0.9207</v>
       </c>
       <c r="G21" t="n">
-        <v>1.4324</v>
+        <v>-0.3641</v>
       </c>
       <c r="H21" t="n">
-        <v>1.3387</v>
+        <v>0.0073</v>
       </c>
       <c r="I21" t="n">
-        <v>0.09370000000000001</v>
+        <v>-0.3714</v>
       </c>
       <c r="J21" t="n">
-        <v>3.048</v>
+        <v>0.9939</v>
       </c>
       <c r="K21" t="n">
-        <v>1.4788</v>
+        <v>0.0504</v>
       </c>
       <c r="L21" t="n">
-        <v>1.5692</v>
+        <v>0.9435</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.6156</v>
+        <v>-1.3581</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.1401</v>
+        <v>-0.0431</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.4755</v>
+        <v>-1.3149</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.8556</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.4793</v>
+        <v>-1.1598</v>
       </c>
       <c r="R21" t="n">
-        <v>1.6237</v>
+        <v>0.6959</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.847</v>
+        <v>0.1858</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8215</v>
+        <v>0.4443</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0255</v>
+        <v>-0.2585</v>
       </c>
       <c r="V21" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. PAJOLA</t>
+          <t>M. DIOUF</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.5856</v>
+        <v>-0.6915</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.9869</v>
+        <v>0.9484</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.5987</v>
+        <v>-1.6398</v>
       </c>
       <c r="G22" t="n">
-        <v>0.1738</v>
+        <v>-1.5035</v>
       </c>
       <c r="H22" t="n">
-        <v>1.7731</v>
+        <v>1.1932</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.5993</v>
+        <v>-2.6967</v>
       </c>
       <c r="J22" t="n">
-        <v>0.7703</v>
+        <v>0.8299</v>
       </c>
       <c r="K22" t="n">
-        <v>1.6805</v>
+        <v>0.6827</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.9102</v>
+        <v>0.1472</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.5965</v>
+        <v>-2.3334</v>
       </c>
       <c r="N22" t="n">
-        <v>0.0926</v>
+        <v>0.5105</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.6891</v>
+        <v>-2.8439</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.6959</v>
+        <v>1.1598</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.4639</v>
+        <v>1.1598</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.0635</v>
+        <v>0.5827</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5975</v>
+        <v>-0.0233</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4661</v>
+        <v>0.606</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-0.9304</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.9383</v>
+        <v>-3.6295</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.9475</v>
+        <v>-2.3013</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.9909</v>
+        <v>-1.3282</v>
       </c>
       <c r="G23" t="n">
         <v>0.019</v>
@@ -2248,13 +2248,13 @@
         <v>1.1598</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0813</v>
+        <v>0.3901</v>
       </c>
       <c r="T23" t="n">
-        <v>0.6765</v>
+        <v>0.3227</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5952</v>
+        <v>0.0674</v>
       </c>
       <c r="V23" t="n">
         <v>-1.719</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.0845</v>
+        <v>-4.1181</v>
       </c>
       <c r="E24" t="n">
         <v>-3.2174</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.8671</v>
+        <v>-0.9006999999999999</v>
       </c>
       <c r="G24" t="n">
         <v>-2.6216</v>
@@ -2326,13 +2326,13 @@
         <v>1.3917</v>
       </c>
       <c r="S24" t="n">
-        <v>0.1428</v>
+        <v>0.1092</v>
       </c>
       <c r="T24" t="n">
         <v>-0.1098</v>
       </c>
       <c r="U24" t="n">
-        <v>0.2526</v>
+        <v>0.219</v>
       </c>
       <c r="V24" t="n">
         <v>-0.6778999999999999</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.9892</v>
+        <v>-0.8440000000000012</v>
       </c>
       <c r="E25" t="n">
-        <v>1.8075</v>
+        <v>1.8077</v>
       </c>
       <c r="F25" t="n">
-        <v>-5.7968</v>
+        <v>-2.6513</v>
       </c>
       <c r="G25" t="n">
         <v>-0.8708000000000005</v>
@@ -2383,7 +2383,7 @@
         <v>7.5305</v>
       </c>
       <c r="L25" t="n">
-        <v>2.6593</v>
+        <v>2.659299999999999</v>
       </c>
       <c r="M25" t="n">
         <v>-11.0607</v>
@@ -2404,13 +2404,13 @@
         <v>10.4381</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.1185999999999998</v>
+        <v>3.0267</v>
       </c>
       <c r="T25" t="n">
         <v>1.555</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.6737</v>
+        <v>1.4716</v>
       </c>
       <c r="V25" t="n">
         <v>1.6394</v>
